--- a/mejoramientoREGISTROSMOD/licencias/FORMATODATOS.xlsx
+++ b/mejoramientoREGISTROSMOD/licencias/FORMATODATOS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivan\Documents\gitdocs-2026\mejoramientoREGISTROSMOD\licencias\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ubicacion C a D\Documentos\gitdocs-2026\mejoramientoREGISTROSMOD\licencias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5CD1834-5465-4228-B266-818E6B9A668A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADF2F260-68C2-46F4-BB7E-4AF51D1793AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{60CAAE2D-5B6B-4BA9-A8AD-B3837DA37C50}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{60CAAE2D-5B6B-4BA9-A8AD-B3837DA37C50}"/>
   </bookViews>
   <sheets>
     <sheet name="H1" sheetId="1" r:id="rId1"/>
@@ -1145,9 +1145,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0B29F7D-79C0-4150-8F5C-F3D352A9CDCB}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="A1:AK30"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:35" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:35" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>26</v>
       </c>
@@ -1254,7 +1254,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:35" ht="57" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" ht="60" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>2023</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>45044</v>
       </c>
     </row>
-    <row r="3" spans="1:35" ht="57" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" ht="60" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2023</v>
       </c>
@@ -1444,7 +1444,7 @@
         <v>45044</v>
       </c>
     </row>
-    <row r="4" spans="1:35" ht="71.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" ht="75" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2023</v>
       </c>
@@ -1525,7 +1525,7 @@
       <c r="AH4" s="2"/>
       <c r="AI4" s="5"/>
     </row>
-    <row r="5" spans="1:35" ht="71.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" ht="75" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>2023</v>
       </c>
@@ -1622,7 +1622,7 @@
         <v>45071</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:35" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>2022</v>
       </c>
@@ -1713,7 +1713,7 @@
         <v>44932</v>
       </c>
     </row>
-    <row r="7" spans="1:35" ht="57" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" ht="60" x14ac:dyDescent="0.3">
       <c r="A7" s="10">
         <v>2023</v>
       </c>
@@ -1808,7 +1808,7 @@
         <v>45044</v>
       </c>
     </row>
-    <row r="19" spans="1:37" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:37" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
         <v>25</v>
       </c>
@@ -1918,7 +1918,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:37" ht="57" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:37" ht="60" x14ac:dyDescent="0.3">
       <c r="A20" s="9"/>
       <c r="B20" s="10">
         <v>2023</v>
@@ -2014,7 +2014,7 @@
         <v>45044</v>
       </c>
     </row>
-    <row r="26" spans="1:37" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:37" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
         <v>26</v>
       </c>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="AJ26" s="13"/>
     </row>
-    <row r="27" spans="1:37" ht="57" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:37" ht="60" x14ac:dyDescent="0.3">
       <c r="A27" s="9"/>
       <c r="B27" s="10">
         <v>2023</v>
@@ -2218,7 +2218,7 @@
         <v>45044</v>
       </c>
     </row>
-    <row r="29" spans="1:37" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:37" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B29" s="6" t="s">
         <v>26</v>
       </c>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="AK29" s="13"/>
     </row>
-    <row r="30" spans="1:37" ht="57" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:37" ht="60" x14ac:dyDescent="0.3">
       <c r="B30" s="9"/>
       <c r="C30" s="10">
         <v>2023</v>
@@ -2437,29 +2437,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7135380C-80D6-4B0E-897D-69116AC42242}">
   <sheetPr codeName="Hoja2"/>
   <dimension ref="A1:BO12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.140625" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" customWidth="1"/>
-    <col min="3" max="3" width="48.28515625" customWidth="1"/>
-    <col min="4" max="4" width="34.140625" customWidth="1"/>
-    <col min="5" max="5" width="31.28515625" customWidth="1"/>
+    <col min="1" max="1" width="16.109375" customWidth="1"/>
+    <col min="2" max="2" width="21.33203125" customWidth="1"/>
+    <col min="3" max="3" width="48.33203125" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="5" max="5" width="31.33203125" customWidth="1"/>
     <col min="9" max="9" width="15" customWidth="1"/>
     <col min="12" max="12" width="31" customWidth="1"/>
-    <col min="16" max="16" width="31.5703125" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" customWidth="1"/>
-    <col min="22" max="22" width="27.85546875" customWidth="1"/>
+    <col min="16" max="16" width="31.5546875" customWidth="1"/>
+    <col min="21" max="21" width="14.88671875" customWidth="1"/>
+    <col min="22" max="22" width="27.88671875" customWidth="1"/>
     <col min="23" max="23" width="19" customWidth="1"/>
-    <col min="24" max="24" width="21.42578125" customWidth="1"/>
+    <col min="24" max="24" width="21.44140625" customWidth="1"/>
     <col min="26" max="26" width="16" customWidth="1"/>
-    <col min="46" max="46" width="14.7109375" customWidth="1"/>
-    <col min="47" max="47" width="38.85546875" customWidth="1"/>
-    <col min="58" max="58" width="20.42578125" customWidth="1"/>
-    <col min="59" max="59" width="19.28515625" customWidth="1"/>
-    <col min="60" max="60" width="16.5703125" customWidth="1"/>
+    <col min="46" max="46" width="14.6640625" customWidth="1"/>
+    <col min="47" max="47" width="38.88671875" customWidth="1"/>
+    <col min="58" max="58" width="20.44140625" customWidth="1"/>
+    <col min="59" max="59" width="19.33203125" customWidth="1"/>
+    <col min="60" max="60" width="16.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:67" s="19" customFormat="1" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:67" s="19" customFormat="1" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>82</v>
       </c>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="BO1" s="17"/>
     </row>
-    <row r="2" spans="1:67" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:67" ht="15" x14ac:dyDescent="0.3">
       <c r="A2" t="str">
         <f>'H1'!Z2</f>
         <v>L23-258-RL001</v>
@@ -2784,7 +2784,7 @@
         <v>LUS23-231-RL001</v>
       </c>
     </row>
-    <row r="3" spans="1:67" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:67" x14ac:dyDescent="0.3">
       <c r="C3" t="str">
         <f>IF(
 OR(ISNUMBER(SEARCH("Y CDUEÑOS",'H1'!H3)),ISNUMBER(SEARCH("Y CONDUEÑOS",'H1'!H3))),
@@ -2801,7 +2801,7 @@
         <v>WOTZBELI EUGENIO LIMATUJ IXCARAGUA</v>
       </c>
     </row>
-    <row r="4" spans="1:67" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:67" x14ac:dyDescent="0.3">
       <c r="C4" t="str">
         <f>IF(
 OR(ISNUMBER(SEARCH("Y CDUEÑOS",'H1'!H4)),ISNUMBER(SEARCH("Y CONDUEÑOS",'H1'!H4))),
@@ -2818,7 +2818,7 @@
         <v>ANA MARIA N. SUASNAVAR BOLAÑOS Y CDUEÑOS</v>
       </c>
     </row>
-    <row r="5" spans="1:67" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:67" x14ac:dyDescent="0.3">
       <c r="C5" t="str">
         <f>IF(
 OR(ISNUMBER(SEARCH("Y CDUEÑOS",'H1'!H5)),ISNUMBER(SEARCH("Y CONDUEÑOS",'H1'!H5))),
@@ -2835,7 +2835,7 @@
         <v>JOSUE MANUEL GONZALEZ MENDEZ</v>
       </c>
     </row>
-    <row r="6" spans="1:67" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:67" x14ac:dyDescent="0.3">
       <c r="C6" t="str">
         <f>IF(
 OR(ISNUMBER(SEARCH("Y CDUEÑOS",'H1'!H6)),ISNUMBER(SEARCH("Y CONDUEÑOS",'H1'!H6))),
@@ -2852,13 +2852,13 @@
         <v>BETZABE LIMA DE SERRANO ESTER</v>
       </c>
     </row>
-    <row r="7" spans="1:67" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:67" x14ac:dyDescent="0.3">
       <c r="C7" t="str">
         <f>TRIM(MID('H1'!H7,SEARCH(" ",'H1'!H7,SEARCH(" ",'H1'!H7)+1)+1,999)&amp;" "&amp;LEFT('H1'!H7,SEARCH(" ",'H1'!H7,SEARCH(" ",'H1'!H7)+1)-1))</f>
         <v>WOTZBELI EUGENIO LIMATUJ IXCARAGUA</v>
       </c>
     </row>
-    <row r="12" spans="1:67" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:67" x14ac:dyDescent="0.3">
       <c r="D12" s="24"/>
     </row>
   </sheetData>
